--- a/results/reliability_eval/Llama-3-8B_P108_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P108_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6045029329847335</v>
+        <v>0.5344027963170068</v>
       </c>
       <c r="B2" t="n">
-        <v>0.665272975022986</v>
+        <v>0.5545540789214181</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6045029329847335</v>
+        <v>0.5344027963170068</v>
       </c>
       <c r="D2" t="n">
-        <v>0.665272975022986</v>
+        <v>0.5545540789214181</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3920082931236184</v>
+        <v>0.48772001555291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5207168968327928</v>
+        <v>0.5339702620871519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9977747617600408</v>
+        <v>0.9915400988491647</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9980293914818938</v>
+        <v>0.9908828598499491</v>
       </c>
       <c r="I2" t="n">
-        <v>0.599</v>
+        <v>0.523</v>
       </c>
     </row>
   </sheetData>
